--- a/实验数据/国债-上证五年期国债.xlsx
+++ b/实验数据/国债-上证五年期国债.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zhang Xijin\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\D\复权软件\实验数据\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6744C4C3-B497-4032-BF4C-C1DFB4D45496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00666B87-CB8E-4238-A3C9-1BD340F14A19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -84,7 +84,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>date</t>
+    <t>日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
